--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,15 +362,6 @@
     <t>fr-lm-section.subSection</t>
   </si>
   <si>
-    <t>fr-lm-examination-report.entry</t>
-  </si>
-  <si>
-    <t>Entrées</t>
-  </si>
-  <si>
-    <t>fr-lm-section.entry</t>
-  </si>
-  <si>
     <t>fr-lm-examination-report.subSection.conclusion</t>
   </si>
   <si>
@@ -379,6 +370,15 @@
   </si>
   <si>
     <t>Conclusion de l'examen</t>
+  </si>
+  <si>
+    <t>fr-lm-examination-report.entry</t>
+  </si>
+  <si>
+    <t>Entrées</t>
+  </si>
+  <si>
+    <t>fr-lm-section.entry</t>
   </si>
   <si>
     <t>fr-lm-examination-report.entry.imagingProcedures</t>
@@ -1886,7 +1886,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1898,13 +1898,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1955,13 +1955,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -1986,7 +1986,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -1998,13 +1998,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>118</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2055,13 +2055,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>

--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
